--- a/data/processed/market/vix_data.xlsx
+++ b/data/processed/market/vix_data.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,80 +449,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46063</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>17.79000091552734</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="C2" t="n">
-        <v>17.96999931335449</v>
+        <v>20.54000091552734</v>
       </c>
       <c r="D2" t="n">
-        <v>17.13999938964844</v>
+        <v>17.5</v>
       </c>
       <c r="E2" t="n">
-        <v>17.46999931335449</v>
+        <v>18.06999969482422</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46064</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>17.64999961853027</v>
+        <v>19.86000061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>18.95999908447266</v>
+        <v>21.73999977111816</v>
       </c>
       <c r="D3" t="n">
-        <v>16.75</v>
+        <v>18.77000045776367</v>
       </c>
       <c r="E3" t="n">
-        <v>17.8700008392334</v>
+        <v>19.28000068664551</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46065</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>20.81999969482422</v>
+        <v>21.44000053405762</v>
       </c>
       <c r="C4" t="n">
-        <v>21.20999908447266</v>
+        <v>25.23999977111816</v>
       </c>
       <c r="D4" t="n">
-        <v>17.07999992370605</v>
+        <v>20.3700008392334</v>
       </c>
       <c r="E4" t="n">
-        <v>17.44000053405762</v>
+        <v>24.65999984741211</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46066</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>20.60000038146973</v>
+        <v>23.56999969482422</v>
       </c>
       <c r="C5" t="n">
-        <v>22.39999961853027</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="D5" t="n">
-        <v>18.92000007629395</v>
+        <v>22.18000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>21.47999954223633</v>
+        <v>24.56999969482422</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
